--- a/santri/DATA SANTRI MADASA.xlsx
+++ b/santri/DATA SANTRI MADASA.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="668">
   <si>
     <t>TTL</t>
   </si>
@@ -2617,24 +2617,14 @@
       <c r="C2" s="30" t="s">
         <v>666</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>465</v>
-      </c>
+      <c r="D2" s="15"/>
       <c r="E2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>504</v>
-      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
@@ -2646,24 +2636,14 @@
       <c r="C3" s="30" t="s">
         <v>666</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>104</v>
-      </c>
+      <c r="D3" s="16"/>
       <c r="E3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>108</v>
-      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="27">
@@ -2675,24 +2655,14 @@
       <c r="C4" s="30" t="s">
         <v>666</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>483</v>
-      </c>
+      <c r="D4" s="15"/>
       <c r="E4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>262</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>505</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="27">
@@ -2701,7 +2671,9 @@
       <c r="B5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="27"/>
+      <c r="C5" s="27" t="s">
+        <v>667</v>
+      </c>
       <c r="D5" s="12"/>
       <c r="E5" s="14" t="s">
         <v>17</v>
@@ -2718,7 +2690,9 @@
       <c r="B6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="27" t="s">
+        <v>667</v>
+      </c>
       <c r="D6" s="12"/>
       <c r="E6" s="14" t="s">
         <v>17</v>
